--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120133127</v>
+        <v>120132212</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>101249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587132</v>
+        <v>587156</v>
       </c>
       <c r="R2" t="n">
-        <v>6552431</v>
+        <v>6552379</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B3" t="n">
         <v>108787</v>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R3" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120132212</v>
+        <v>120133276</v>
       </c>
       <c r="B4" t="n">
-        <v>101249</v>
+        <v>108787</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587156</v>
+        <v>587309</v>
       </c>
       <c r="R4" t="n">
-        <v>6552379</v>
+        <v>6552371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120132212</v>
       </c>
       <c r="B2" t="n">
-        <v>101249</v>
+        <v>101272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133127</v>
+        <v>120133276</v>
       </c>
       <c r="B3" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587132</v>
+        <v>587309</v>
       </c>
       <c r="R3" t="n">
-        <v>6552431</v>
+        <v>6552371</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B4" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R4" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120132212</v>
+        <v>120133127</v>
       </c>
       <c r="B2" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587156</v>
+        <v>587132</v>
       </c>
       <c r="R2" t="n">
-        <v>6552379</v>
+        <v>6552431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120133127</v>
+        <v>120132212</v>
       </c>
       <c r="B4" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587132</v>
+        <v>587156</v>
       </c>
       <c r="R4" t="n">
-        <v>6552431</v>
+        <v>6552379</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120133127</v>
+        <v>120133276</v>
       </c>
       <c r="B2" t="n">
         <v>108811</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587132</v>
+        <v>587309</v>
       </c>
       <c r="R2" t="n">
-        <v>6552431</v>
+        <v>6552371</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B3" t="n">
         <v>108811</v>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R3" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B2" t="n">
         <v>108811</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R2" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133127</v>
+        <v>120133276</v>
       </c>
       <c r="B3" t="n">
         <v>108811</v>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587132</v>
+        <v>587309</v>
       </c>
       <c r="R3" t="n">
-        <v>6552431</v>
+        <v>6552371</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120133127</v>
+        <v>120132212</v>
       </c>
       <c r="B2" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587132</v>
+        <v>587156</v>
       </c>
       <c r="R2" t="n">
-        <v>6552431</v>
+        <v>6552379</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B3" t="n">
         <v>108811</v>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R3" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120132212</v>
+        <v>120133276</v>
       </c>
       <c r="B4" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587156</v>
+        <v>587309</v>
       </c>
       <c r="R4" t="n">
-        <v>6552379</v>
+        <v>6552371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120132212</v>
+        <v>120133276</v>
       </c>
       <c r="B2" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587156</v>
+        <v>587309</v>
       </c>
       <c r="R2" t="n">
-        <v>6552379</v>
+        <v>6552371</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133127</v>
+        <v>120132212</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587132</v>
+        <v>587156</v>
       </c>
       <c r="R3" t="n">
-        <v>6552431</v>
+        <v>6552379</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120133276</v>
+        <v>120133127</v>
       </c>
       <c r="B4" t="n">
         <v>108811</v>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587309</v>
+        <v>587132</v>
       </c>
       <c r="R4" t="n">
-        <v>6552371</v>
+        <v>6552431</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120132212</v>
+        <v>120133127</v>
       </c>
       <c r="B3" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587156</v>
+        <v>587132</v>
       </c>
       <c r="R3" t="n">
-        <v>6552379</v>
+        <v>6552431</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120133127</v>
+        <v>120132212</v>
       </c>
       <c r="B4" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587132</v>
+        <v>587156</v>
       </c>
       <c r="R4" t="n">
-        <v>6552431</v>
+        <v>6552379</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120132212</v>
+        <v>120133127</v>
       </c>
       <c r="B2" t="n">
-        <v>101272</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsbäck 250m SSO, Srm</t>
+          <t>Ramsbäck 200m SSO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587156</v>
+        <v>587132</v>
       </c>
       <c r="R2" t="n">
-        <v>6552379</v>
+        <v>6552431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120133127</v>
+        <v>120133276</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,14 +817,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsbäck 200m SSO, Srm</t>
+          <t>Ramsbäck 400m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587132</v>
+        <v>587309</v>
       </c>
       <c r="R3" t="n">
-        <v>6552431</v>
+        <v>6552371</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120133276</v>
+        <v>120132212</v>
       </c>
       <c r="B4" t="n">
-        <v>108811</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +924,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsbäck 400m SO, Srm</t>
+          <t>Ramsbäck 250m SSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587309</v>
+        <v>587156</v>
       </c>
       <c r="R4" t="n">
-        <v>6552371</v>
+        <v>6552379</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +978,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47194-2022 artfynd.xlsx
+++ b/artfynd/A 47194-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120133127</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120133276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120132212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>